--- a/plantillas/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores.xlsx
@@ -203,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -217,7 +217,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -238,8 +240,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -675,6 +684,7 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -722,6 +732,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
@@ -753,6 +764,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="n"/>
       <c r="B21" s="13" t="n"/>
@@ -767,6 +779,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -831,6 +844,7 @@
       <c r="I2" s="18" t="n"/>
       <c r="J2" s="19" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
@@ -841,6 +855,7 @@
       <c r="C4" s="9" t="n"/>
       <c r="D4" s="9" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
@@ -894,7 +909,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="22" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="9" t="n"/>
@@ -903,12 +918,12 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="24" t="n"/>
       <c r="J7" s="9" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="22" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="9" t="n"/>
@@ -917,12 +932,12 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="24" t="n"/>
       <c r="J8" s="9" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="22" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="9" t="n"/>
@@ -931,12 +946,12 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="24" t="n"/>
       <c r="J9" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="22" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="9" t="n"/>
@@ -945,12 +960,12 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
       <c r="G10" s="9" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="24" t="n"/>
       <c r="J10" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="22" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="9" t="n"/>
@@ -959,12 +974,12 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="23" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="24" t="n"/>
       <c r="J11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="22" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -973,12 +988,12 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
       <c r="G12" s="9" t="n"/>
-      <c r="H12" s="22" t="n"/>
-      <c r="I12" s="23" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="24" t="n"/>
       <c r="J12" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="22" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -987,12 +1002,12 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="22" t="n"/>
-      <c r="I13" s="23" t="n"/>
+      <c r="H13" s="23" t="n"/>
+      <c r="I13" s="24" t="n"/>
       <c r="J13" s="9" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="22" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="9" t="n"/>
@@ -1001,12 +1016,12 @@
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="9" t="n"/>
-      <c r="H14" s="22" t="n"/>
-      <c r="I14" s="23" t="n"/>
+      <c r="H14" s="23" t="n"/>
+      <c r="I14" s="24" t="n"/>
       <c r="J14" s="9" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="22" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="9" t="n"/>
@@ -1015,12 +1030,12 @@
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="24" t="n"/>
       <c r="J15" s="9" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="22" t="n">
         <v>10</v>
       </c>
       <c r="B16" s="9" t="n"/>
@@ -1029,12 +1044,12 @@
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="9" t="n"/>
       <c r="G16" s="9" t="n"/>
-      <c r="H16" s="22" t="n"/>
-      <c r="I16" s="23" t="n"/>
+      <c r="H16" s="23" t="n"/>
+      <c r="I16" s="24" t="n"/>
       <c r="J16" s="9" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="22" t="n">
         <v>11</v>
       </c>
       <c r="B17" s="9" t="n"/>
@@ -1043,12 +1058,12 @@
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n"/>
-      <c r="H17" s="22" t="n"/>
-      <c r="I17" s="23" t="n"/>
+      <c r="H17" s="23" t="n"/>
+      <c r="I17" s="24" t="n"/>
       <c r="J17" s="9" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="22" t="n">
         <v>12</v>
       </c>
       <c r="B18" s="9" t="n"/>
@@ -1057,12 +1072,12 @@
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="9" t="n"/>
       <c r="G18" s="9" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="23" t="n"/>
+      <c r="H18" s="23" t="n"/>
+      <c r="I18" s="24" t="n"/>
       <c r="J18" s="9" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="22" t="n">
         <v>13</v>
       </c>
       <c r="B19" s="9" t="n"/>
@@ -1071,12 +1086,12 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="23" t="n"/>
+      <c r="H19" s="23" t="n"/>
+      <c r="I19" s="24" t="n"/>
       <c r="J19" s="9" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="22" t="n">
         <v>14</v>
       </c>
       <c r="B20" s="9" t="n"/>
@@ -1085,12 +1100,12 @@
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
       <c r="G20" s="9" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="23" t="n"/>
+      <c r="H20" s="23" t="n"/>
+      <c r="I20" s="24" t="n"/>
       <c r="J20" s="9" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="22" t="n">
         <v>15</v>
       </c>
       <c r="B21" s="9" t="n"/>
@@ -1099,12 +1114,12 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="22" t="n"/>
-      <c r="I21" s="23" t="n"/>
+      <c r="H21" s="23" t="n"/>
+      <c r="I21" s="24" t="n"/>
       <c r="J21" s="9" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="22" t="n">
         <v>16</v>
       </c>
       <c r="B22" s="9" t="n"/>
@@ -1113,12 +1128,12 @@
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
       <c r="G22" s="9" t="n"/>
-      <c r="H22" s="22" t="n"/>
-      <c r="I22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="24" t="n"/>
       <c r="J22" s="9" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="22" t="n">
         <v>17</v>
       </c>
       <c r="B23" s="9" t="n"/>
@@ -1127,12 +1142,12 @@
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
-      <c r="H23" s="22" t="n"/>
-      <c r="I23" s="23" t="n"/>
+      <c r="H23" s="23" t="n"/>
+      <c r="I23" s="24" t="n"/>
       <c r="J23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="22" t="n">
         <v>18</v>
       </c>
       <c r="B24" s="9" t="n"/>
@@ -1141,12 +1156,12 @@
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
       <c r="G24" s="9" t="n"/>
-      <c r="H24" s="22" t="n"/>
-      <c r="I24" s="23" t="n"/>
+      <c r="H24" s="23" t="n"/>
+      <c r="I24" s="24" t="n"/>
       <c r="J24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="22" t="n">
         <v>19</v>
       </c>
       <c r="B25" s="9" t="n"/>
@@ -1155,12 +1170,12 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
-      <c r="H25" s="22" t="n"/>
-      <c r="I25" s="23" t="n"/>
+      <c r="H25" s="23" t="n"/>
+      <c r="I25" s="24" t="n"/>
       <c r="J25" s="9" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="22" t="n">
         <v>20</v>
       </c>
       <c r="B26" s="9" t="n"/>
@@ -1169,12 +1184,12 @@
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="9" t="n"/>
       <c r="G26" s="9" t="n"/>
-      <c r="H26" s="22" t="n"/>
-      <c r="I26" s="23" t="n"/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="24" t="n"/>
       <c r="J26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="22" t="n">
         <v>21</v>
       </c>
       <c r="B27" s="9" t="n"/>
@@ -1183,12 +1198,12 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="22" t="n"/>
-      <c r="I27" s="23" t="n"/>
+      <c r="H27" s="23" t="n"/>
+      <c r="I27" s="24" t="n"/>
       <c r="J27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="22" t="n">
         <v>22</v>
       </c>
       <c r="B28" s="9" t="n"/>
@@ -1197,12 +1212,12 @@
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="9" t="n"/>
       <c r="G28" s="9" t="n"/>
-      <c r="H28" s="22" t="n"/>
-      <c r="I28" s="23" t="n"/>
+      <c r="H28" s="23" t="n"/>
+      <c r="I28" s="24" t="n"/>
       <c r="J28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="22" t="n">
         <v>23</v>
       </c>
       <c r="B29" s="9" t="n"/>
@@ -1211,12 +1226,12 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="9" t="n"/>
       <c r="G29" s="9" t="n"/>
-      <c r="H29" s="22" t="n"/>
-      <c r="I29" s="23" t="n"/>
+      <c r="H29" s="23" t="n"/>
+      <c r="I29" s="24" t="n"/>
       <c r="J29" s="9" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="22" t="n">
         <v>24</v>
       </c>
       <c r="B30" s="9" t="n"/>
@@ -1225,12 +1240,12 @@
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="9" t="n"/>
       <c r="G30" s="9" t="n"/>
-      <c r="H30" s="22" t="n"/>
-      <c r="I30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="24" t="n"/>
       <c r="J30" s="9" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="22" t="n">
         <v>25</v>
       </c>
       <c r="B31" s="9" t="n"/>
@@ -1239,12 +1254,12 @@
       <c r="E31" s="9" t="n"/>
       <c r="F31" s="9" t="n"/>
       <c r="G31" s="9" t="n"/>
-      <c r="H31" s="22" t="n"/>
-      <c r="I31" s="23" t="n"/>
+      <c r="H31" s="23" t="n"/>
+      <c r="I31" s="24" t="n"/>
       <c r="J31" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="22" t="n">
         <v>26</v>
       </c>
       <c r="B32" s="9" t="n"/>
@@ -1253,12 +1268,12 @@
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="9" t="n"/>
       <c r="G32" s="9" t="n"/>
-      <c r="H32" s="22" t="n"/>
-      <c r="I32" s="23" t="n"/>
+      <c r="H32" s="23" t="n"/>
+      <c r="I32" s="24" t="n"/>
       <c r="J32" s="9" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="22" t="n">
         <v>27</v>
       </c>
       <c r="B33" s="9" t="n"/>
@@ -1267,12 +1282,12 @@
       <c r="E33" s="9" t="n"/>
       <c r="F33" s="9" t="n"/>
       <c r="G33" s="9" t="n"/>
-      <c r="H33" s="22" t="n"/>
-      <c r="I33" s="23" t="n"/>
+      <c r="H33" s="23" t="n"/>
+      <c r="I33" s="24" t="n"/>
       <c r="J33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="22" t="n">
         <v>28</v>
       </c>
       <c r="B34" s="9" t="n"/>
@@ -1281,12 +1296,12 @@
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n"/>
-      <c r="H34" s="22" t="n"/>
-      <c r="I34" s="23" t="n"/>
+      <c r="H34" s="23" t="n"/>
+      <c r="I34" s="24" t="n"/>
       <c r="J34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="22" t="n">
         <v>29</v>
       </c>
       <c r="B35" s="9" t="n"/>
@@ -1295,12 +1310,12 @@
       <c r="E35" s="9" t="n"/>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n"/>
-      <c r="H35" s="22" t="n"/>
-      <c r="I35" s="23" t="n"/>
+      <c r="H35" s="23" t="n"/>
+      <c r="I35" s="24" t="n"/>
       <c r="J35" s="9" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="22" t="n">
         <v>30</v>
       </c>
       <c r="B36" s="9" t="n"/>
@@ -1309,12 +1324,12 @@
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="9" t="n"/>
       <c r="G36" s="9" t="n"/>
-      <c r="H36" s="22" t="n"/>
-      <c r="I36" s="23" t="n"/>
+      <c r="H36" s="23" t="n"/>
+      <c r="I36" s="24" t="n"/>
       <c r="J36" s="9" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="22" t="n">
         <v>31</v>
       </c>
       <c r="B37" s="9" t="n"/>
@@ -1323,12 +1338,12 @@
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="9" t="n"/>
       <c r="G37" s="9" t="n"/>
-      <c r="H37" s="22" t="n"/>
-      <c r="I37" s="23" t="n"/>
+      <c r="H37" s="23" t="n"/>
+      <c r="I37" s="24" t="n"/>
       <c r="J37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="n">
+      <c r="A38" s="22" t="n">
         <v>32</v>
       </c>
       <c r="B38" s="9" t="n"/>
@@ -1337,12 +1352,12 @@
       <c r="E38" s="9" t="n"/>
       <c r="F38" s="9" t="n"/>
       <c r="G38" s="9" t="n"/>
-      <c r="H38" s="22" t="n"/>
-      <c r="I38" s="23" t="n"/>
+      <c r="H38" s="23" t="n"/>
+      <c r="I38" s="24" t="n"/>
       <c r="J38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="n">
+      <c r="A39" s="22" t="n">
         <v>33</v>
       </c>
       <c r="B39" s="9" t="n"/>
@@ -1351,12 +1366,12 @@
       <c r="E39" s="9" t="n"/>
       <c r="F39" s="9" t="n"/>
       <c r="G39" s="9" t="n"/>
-      <c r="H39" s="22" t="n"/>
-      <c r="I39" s="23" t="n"/>
+      <c r="H39" s="23" t="n"/>
+      <c r="I39" s="24" t="n"/>
       <c r="J39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="n">
+      <c r="A40" s="22" t="n">
         <v>34</v>
       </c>
       <c r="B40" s="9" t="n"/>
@@ -1365,12 +1380,12 @@
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="9" t="n"/>
       <c r="G40" s="9" t="n"/>
-      <c r="H40" s="22" t="n"/>
-      <c r="I40" s="23" t="n"/>
+      <c r="H40" s="23" t="n"/>
+      <c r="I40" s="24" t="n"/>
       <c r="J40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="n">
+      <c r="A41" s="22" t="n">
         <v>35</v>
       </c>
       <c r="B41" s="9" t="n"/>
@@ -1379,12 +1394,12 @@
       <c r="E41" s="9" t="n"/>
       <c r="F41" s="9" t="n"/>
       <c r="G41" s="9" t="n"/>
-      <c r="H41" s="22" t="n"/>
-      <c r="I41" s="23" t="n"/>
+      <c r="H41" s="23" t="n"/>
+      <c r="I41" s="24" t="n"/>
       <c r="J41" s="9" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="n">
+      <c r="A42" s="22" t="n">
         <v>36</v>
       </c>
       <c r="B42" s="9" t="n"/>
@@ -1393,12 +1408,12 @@
       <c r="E42" s="9" t="n"/>
       <c r="F42" s="9" t="n"/>
       <c r="G42" s="9" t="n"/>
-      <c r="H42" s="22" t="n"/>
-      <c r="I42" s="23" t="n"/>
+      <c r="H42" s="23" t="n"/>
+      <c r="I42" s="24" t="n"/>
       <c r="J42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="n">
+      <c r="A43" s="22" t="n">
         <v>37</v>
       </c>
       <c r="B43" s="9" t="n"/>
@@ -1407,12 +1422,12 @@
       <c r="E43" s="9" t="n"/>
       <c r="F43" s="9" t="n"/>
       <c r="G43" s="9" t="n"/>
-      <c r="H43" s="22" t="n"/>
-      <c r="I43" s="23" t="n"/>
+      <c r="H43" s="23" t="n"/>
+      <c r="I43" s="24" t="n"/>
       <c r="J43" s="9" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="n">
+      <c r="A44" s="22" t="n">
         <v>38</v>
       </c>
       <c r="B44" s="9" t="n"/>
@@ -1421,12 +1436,12 @@
       <c r="E44" s="9" t="n"/>
       <c r="F44" s="9" t="n"/>
       <c r="G44" s="9" t="n"/>
-      <c r="H44" s="22" t="n"/>
-      <c r="I44" s="23" t="n"/>
+      <c r="H44" s="23" t="n"/>
+      <c r="I44" s="24" t="n"/>
       <c r="J44" s="9" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="n">
+      <c r="A45" s="22" t="n">
         <v>39</v>
       </c>
       <c r="B45" s="9" t="n"/>
@@ -1435,12 +1450,12 @@
       <c r="E45" s="9" t="n"/>
       <c r="F45" s="9" t="n"/>
       <c r="G45" s="9" t="n"/>
-      <c r="H45" s="22" t="n"/>
-      <c r="I45" s="23" t="n"/>
+      <c r="H45" s="23" t="n"/>
+      <c r="I45" s="24" t="n"/>
       <c r="J45" s="9" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="n">
+      <c r="A46" s="22" t="n">
         <v>40</v>
       </c>
       <c r="B46" s="9" t="n"/>
@@ -1449,12 +1464,12 @@
       <c r="E46" s="9" t="n"/>
       <c r="F46" s="9" t="n"/>
       <c r="G46" s="9" t="n"/>
-      <c r="H46" s="22" t="n"/>
-      <c r="I46" s="23" t="n"/>
+      <c r="H46" s="23" t="n"/>
+      <c r="I46" s="24" t="n"/>
       <c r="J46" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="n">
+      <c r="A47" s="22" t="n">
         <v>41</v>
       </c>
       <c r="B47" s="9" t="n"/>
@@ -1463,12 +1478,12 @@
       <c r="E47" s="9" t="n"/>
       <c r="F47" s="9" t="n"/>
       <c r="G47" s="9" t="n"/>
-      <c r="H47" s="22" t="n"/>
-      <c r="I47" s="23" t="n"/>
+      <c r="H47" s="23" t="n"/>
+      <c r="I47" s="24" t="n"/>
       <c r="J47" s="9" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="n">
+      <c r="A48" s="22" t="n">
         <v>42</v>
       </c>
       <c r="B48" s="9" t="n"/>
@@ -1477,12 +1492,12 @@
       <c r="E48" s="9" t="n"/>
       <c r="F48" s="9" t="n"/>
       <c r="G48" s="9" t="n"/>
-      <c r="H48" s="22" t="n"/>
-      <c r="I48" s="23" t="n"/>
+      <c r="H48" s="23" t="n"/>
+      <c r="I48" s="24" t="n"/>
       <c r="J48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="n">
+      <c r="A49" s="22" t="n">
         <v>43</v>
       </c>
       <c r="B49" s="9" t="n"/>
@@ -1491,12 +1506,12 @@
       <c r="E49" s="9" t="n"/>
       <c r="F49" s="9" t="n"/>
       <c r="G49" s="9" t="n"/>
-      <c r="H49" s="22" t="n"/>
-      <c r="I49" s="23" t="n"/>
+      <c r="H49" s="23" t="n"/>
+      <c r="I49" s="24" t="n"/>
       <c r="J49" s="9" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="n">
+      <c r="A50" s="22" t="n">
         <v>44</v>
       </c>
       <c r="B50" s="9" t="n"/>
@@ -1505,12 +1520,12 @@
       <c r="E50" s="9" t="n"/>
       <c r="F50" s="9" t="n"/>
       <c r="G50" s="9" t="n"/>
-      <c r="H50" s="22" t="n"/>
-      <c r="I50" s="23" t="n"/>
+      <c r="H50" s="23" t="n"/>
+      <c r="I50" s="24" t="n"/>
       <c r="J50" s="9" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="n">
+      <c r="A51" s="22" t="n">
         <v>45</v>
       </c>
       <c r="B51" s="9" t="n"/>
@@ -1519,12 +1534,12 @@
       <c r="E51" s="9" t="n"/>
       <c r="F51" s="9" t="n"/>
       <c r="G51" s="9" t="n"/>
-      <c r="H51" s="22" t="n"/>
-      <c r="I51" s="23" t="n"/>
+      <c r="H51" s="23" t="n"/>
+      <c r="I51" s="24" t="n"/>
       <c r="J51" s="9" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="n">
+      <c r="A52" s="22" t="n">
         <v>46</v>
       </c>
       <c r="B52" s="9" t="n"/>
@@ -1533,12 +1548,12 @@
       <c r="E52" s="9" t="n"/>
       <c r="F52" s="9" t="n"/>
       <c r="G52" s="9" t="n"/>
-      <c r="H52" s="22" t="n"/>
-      <c r="I52" s="23" t="n"/>
+      <c r="H52" s="23" t="n"/>
+      <c r="I52" s="24" t="n"/>
       <c r="J52" s="9" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="n">
+      <c r="A53" s="22" t="n">
         <v>47</v>
       </c>
       <c r="B53" s="9" t="n"/>
@@ -1547,12 +1562,12 @@
       <c r="E53" s="9" t="n"/>
       <c r="F53" s="9" t="n"/>
       <c r="G53" s="9" t="n"/>
-      <c r="H53" s="22" t="n"/>
-      <c r="I53" s="23" t="n"/>
+      <c r="H53" s="23" t="n"/>
+      <c r="I53" s="24" t="n"/>
       <c r="J53" s="9" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="n">
+      <c r="A54" s="22" t="n">
         <v>48</v>
       </c>
       <c r="B54" s="9" t="n"/>
@@ -1561,12 +1576,12 @@
       <c r="E54" s="9" t="n"/>
       <c r="F54" s="9" t="n"/>
       <c r="G54" s="9" t="n"/>
-      <c r="H54" s="22" t="n"/>
-      <c r="I54" s="23" t="n"/>
+      <c r="H54" s="23" t="n"/>
+      <c r="I54" s="24" t="n"/>
       <c r="J54" s="9" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="n">
+      <c r="A55" s="22" t="n">
         <v>49</v>
       </c>
       <c r="B55" s="9" t="n"/>
@@ -1575,12 +1590,12 @@
       <c r="E55" s="9" t="n"/>
       <c r="F55" s="9" t="n"/>
       <c r="G55" s="9" t="n"/>
-      <c r="H55" s="22" t="n"/>
-      <c r="I55" s="23" t="n"/>
+      <c r="H55" s="23" t="n"/>
+      <c r="I55" s="24" t="n"/>
       <c r="J55" s="9" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="n">
+      <c r="A56" s="22" t="n">
         <v>50</v>
       </c>
       <c r="B56" s="9" t="n"/>
@@ -1589,12 +1604,12 @@
       <c r="E56" s="9" t="n"/>
       <c r="F56" s="9" t="n"/>
       <c r="G56" s="9" t="n"/>
-      <c r="H56" s="22" t="n"/>
-      <c r="I56" s="23" t="n"/>
+      <c r="H56" s="23" t="n"/>
+      <c r="I56" s="24" t="n"/>
       <c r="J56" s="9" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="n">
+      <c r="A57" s="22" t="n">
         <v>51</v>
       </c>
       <c r="B57" s="9" t="n"/>
@@ -1603,12 +1618,12 @@
       <c r="E57" s="9" t="n"/>
       <c r="F57" s="9" t="n"/>
       <c r="G57" s="9" t="n"/>
-      <c r="H57" s="22" t="n"/>
-      <c r="I57" s="23" t="n"/>
+      <c r="H57" s="23" t="n"/>
+      <c r="I57" s="24" t="n"/>
       <c r="J57" s="9" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="n">
+      <c r="A58" s="22" t="n">
         <v>52</v>
       </c>
       <c r="B58" s="9" t="n"/>
@@ -1617,12 +1632,12 @@
       <c r="E58" s="9" t="n"/>
       <c r="F58" s="9" t="n"/>
       <c r="G58" s="9" t="n"/>
-      <c r="H58" s="22" t="n"/>
-      <c r="I58" s="23" t="n"/>
+      <c r="H58" s="23" t="n"/>
+      <c r="I58" s="24" t="n"/>
       <c r="J58" s="9" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="n">
+      <c r="A59" s="22" t="n">
         <v>53</v>
       </c>
       <c r="B59" s="9" t="n"/>
@@ -1631,12 +1646,12 @@
       <c r="E59" s="9" t="n"/>
       <c r="F59" s="9" t="n"/>
       <c r="G59" s="9" t="n"/>
-      <c r="H59" s="22" t="n"/>
-      <c r="I59" s="23" t="n"/>
+      <c r="H59" s="23" t="n"/>
+      <c r="I59" s="24" t="n"/>
       <c r="J59" s="9" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="n">
+      <c r="A60" s="22" t="n">
         <v>54</v>
       </c>
       <c r="B60" s="9" t="n"/>
@@ -1645,12 +1660,12 @@
       <c r="E60" s="9" t="n"/>
       <c r="F60" s="9" t="n"/>
       <c r="G60" s="9" t="n"/>
-      <c r="H60" s="22" t="n"/>
-      <c r="I60" s="23" t="n"/>
+      <c r="H60" s="23" t="n"/>
+      <c r="I60" s="24" t="n"/>
       <c r="J60" s="9" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="n">
+      <c r="A61" s="22" t="n">
         <v>55</v>
       </c>
       <c r="B61" s="9" t="n"/>
@@ -1659,12 +1674,12 @@
       <c r="E61" s="9" t="n"/>
       <c r="F61" s="9" t="n"/>
       <c r="G61" s="9" t="n"/>
-      <c r="H61" s="22" t="n"/>
-      <c r="I61" s="23" t="n"/>
+      <c r="H61" s="23" t="n"/>
+      <c r="I61" s="24" t="n"/>
       <c r="J61" s="9" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="n">
+      <c r="A62" s="22" t="n">
         <v>56</v>
       </c>
       <c r="B62" s="9" t="n"/>
@@ -1673,12 +1688,12 @@
       <c r="E62" s="9" t="n"/>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="9" t="n"/>
-      <c r="H62" s="22" t="n"/>
-      <c r="I62" s="23" t="n"/>
+      <c r="H62" s="23" t="n"/>
+      <c r="I62" s="24" t="n"/>
       <c r="J62" s="9" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="11" t="n">
+      <c r="A63" s="22" t="n">
         <v>57</v>
       </c>
       <c r="B63" s="9" t="n"/>
@@ -1687,12 +1702,12 @@
       <c r="E63" s="9" t="n"/>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="9" t="n"/>
-      <c r="H63" s="22" t="n"/>
-      <c r="I63" s="23" t="n"/>
+      <c r="H63" s="23" t="n"/>
+      <c r="I63" s="24" t="n"/>
       <c r="J63" s="9" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="11" t="n">
+      <c r="A64" s="22" t="n">
         <v>58</v>
       </c>
       <c r="B64" s="9" t="n"/>
@@ -1701,12 +1716,12 @@
       <c r="E64" s="9" t="n"/>
       <c r="F64" s="9" t="n"/>
       <c r="G64" s="9" t="n"/>
-      <c r="H64" s="22" t="n"/>
-      <c r="I64" s="23" t="n"/>
+      <c r="H64" s="23" t="n"/>
+      <c r="I64" s="24" t="n"/>
       <c r="J64" s="9" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="n">
+      <c r="A65" s="22" t="n">
         <v>59</v>
       </c>
       <c r="B65" s="9" t="n"/>
@@ -1715,12 +1730,12 @@
       <c r="E65" s="9" t="n"/>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="9" t="n"/>
-      <c r="H65" s="22" t="n"/>
-      <c r="I65" s="23" t="n"/>
+      <c r="H65" s="23" t="n"/>
+      <c r="I65" s="24" t="n"/>
       <c r="J65" s="9" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="n">
+      <c r="A66" s="22" t="n">
         <v>60</v>
       </c>
       <c r="B66" s="9" t="n"/>
@@ -1729,12 +1744,12 @@
       <c r="E66" s="9" t="n"/>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="9" t="n"/>
-      <c r="H66" s="22" t="n"/>
-      <c r="I66" s="23" t="n"/>
+      <c r="H66" s="23" t="n"/>
+      <c r="I66" s="24" t="n"/>
       <c r="J66" s="9" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="11" t="n">
+      <c r="A67" s="22" t="n">
         <v>61</v>
       </c>
       <c r="B67" s="9" t="n"/>
@@ -1743,12 +1758,12 @@
       <c r="E67" s="9" t="n"/>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="9" t="n"/>
-      <c r="H67" s="22" t="n"/>
-      <c r="I67" s="23" t="n"/>
+      <c r="H67" s="23" t="n"/>
+      <c r="I67" s="24" t="n"/>
       <c r="J67" s="9" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="n">
+      <c r="A68" s="22" t="n">
         <v>62</v>
       </c>
       <c r="B68" s="9" t="n"/>
@@ -1757,12 +1772,12 @@
       <c r="E68" s="9" t="n"/>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="9" t="n"/>
-      <c r="H68" s="22" t="n"/>
-      <c r="I68" s="23" t="n"/>
+      <c r="H68" s="23" t="n"/>
+      <c r="I68" s="24" t="n"/>
       <c r="J68" s="9" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="11" t="n">
+      <c r="A69" s="22" t="n">
         <v>63</v>
       </c>
       <c r="B69" s="9" t="n"/>
@@ -1771,12 +1786,12 @@
       <c r="E69" s="9" t="n"/>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="9" t="n"/>
-      <c r="H69" s="22" t="n"/>
-      <c r="I69" s="23" t="n"/>
+      <c r="H69" s="23" t="n"/>
+      <c r="I69" s="24" t="n"/>
       <c r="J69" s="9" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="n">
+      <c r="A70" s="22" t="n">
         <v>64</v>
       </c>
       <c r="B70" s="9" t="n"/>
@@ -1785,12 +1800,12 @@
       <c r="E70" s="9" t="n"/>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="9" t="n"/>
-      <c r="H70" s="22" t="n"/>
-      <c r="I70" s="23" t="n"/>
+      <c r="H70" s="23" t="n"/>
+      <c r="I70" s="24" t="n"/>
       <c r="J70" s="9" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="11" t="n">
+      <c r="A71" s="22" t="n">
         <v>65</v>
       </c>
       <c r="B71" s="9" t="n"/>
@@ -1799,12 +1814,12 @@
       <c r="E71" s="9" t="n"/>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="9" t="n"/>
-      <c r="H71" s="22" t="n"/>
-      <c r="I71" s="23" t="n"/>
+      <c r="H71" s="23" t="n"/>
+      <c r="I71" s="24" t="n"/>
       <c r="J71" s="9" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="n">
+      <c r="A72" s="22" t="n">
         <v>66</v>
       </c>
       <c r="B72" s="9" t="n"/>
@@ -1813,12 +1828,12 @@
       <c r="E72" s="9" t="n"/>
       <c r="F72" s="9" t="n"/>
       <c r="G72" s="9" t="n"/>
-      <c r="H72" s="22" t="n"/>
-      <c r="I72" s="23" t="n"/>
+      <c r="H72" s="23" t="n"/>
+      <c r="I72" s="24" t="n"/>
       <c r="J72" s="9" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="11" t="n">
+      <c r="A73" s="22" t="n">
         <v>67</v>
       </c>
       <c r="B73" s="9" t="n"/>
@@ -1827,12 +1842,12 @@
       <c r="E73" s="9" t="n"/>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="9" t="n"/>
-      <c r="H73" s="22" t="n"/>
-      <c r="I73" s="23" t="n"/>
+      <c r="H73" s="23" t="n"/>
+      <c r="I73" s="24" t="n"/>
       <c r="J73" s="9" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="11" t="n">
+      <c r="A74" s="22" t="n">
         <v>68</v>
       </c>
       <c r="B74" s="9" t="n"/>
@@ -1841,12 +1856,12 @@
       <c r="E74" s="9" t="n"/>
       <c r="F74" s="9" t="n"/>
       <c r="G74" s="9" t="n"/>
-      <c r="H74" s="22" t="n"/>
-      <c r="I74" s="23" t="n"/>
+      <c r="H74" s="23" t="n"/>
+      <c r="I74" s="24" t="n"/>
       <c r="J74" s="9" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="11" t="n">
+      <c r="A75" s="22" t="n">
         <v>69</v>
       </c>
       <c r="B75" s="9" t="n"/>
@@ -1855,12 +1870,12 @@
       <c r="E75" s="9" t="n"/>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="9" t="n"/>
-      <c r="H75" s="22" t="n"/>
-      <c r="I75" s="23" t="n"/>
+      <c r="H75" s="23" t="n"/>
+      <c r="I75" s="24" t="n"/>
       <c r="J75" s="9" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="11" t="n">
+      <c r="A76" s="22" t="n">
         <v>70</v>
       </c>
       <c r="B76" s="9" t="n"/>
@@ -1869,12 +1884,12 @@
       <c r="E76" s="9" t="n"/>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="9" t="n"/>
-      <c r="H76" s="22" t="n"/>
-      <c r="I76" s="23" t="n"/>
+      <c r="H76" s="23" t="n"/>
+      <c r="I76" s="24" t="n"/>
       <c r="J76" s="9" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="n">
+      <c r="A77" s="22" t="n">
         <v>71</v>
       </c>
       <c r="B77" s="9" t="n"/>
@@ -1883,12 +1898,12 @@
       <c r="E77" s="9" t="n"/>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="9" t="n"/>
-      <c r="H77" s="22" t="n"/>
-      <c r="I77" s="23" t="n"/>
+      <c r="H77" s="23" t="n"/>
+      <c r="I77" s="24" t="n"/>
       <c r="J77" s="9" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="11" t="n">
+      <c r="A78" s="22" t="n">
         <v>72</v>
       </c>
       <c r="B78" s="9" t="n"/>
@@ -1897,12 +1912,12 @@
       <c r="E78" s="9" t="n"/>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="9" t="n"/>
-      <c r="H78" s="22" t="n"/>
-      <c r="I78" s="23" t="n"/>
+      <c r="H78" s="23" t="n"/>
+      <c r="I78" s="24" t="n"/>
       <c r="J78" s="9" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="11" t="n">
+      <c r="A79" s="22" t="n">
         <v>73</v>
       </c>
       <c r="B79" s="9" t="n"/>
@@ -1911,12 +1926,12 @@
       <c r="E79" s="9" t="n"/>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="9" t="n"/>
-      <c r="H79" s="22" t="n"/>
-      <c r="I79" s="23" t="n"/>
+      <c r="H79" s="23" t="n"/>
+      <c r="I79" s="24" t="n"/>
       <c r="J79" s="9" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="n">
+      <c r="A80" s="22" t="n">
         <v>74</v>
       </c>
       <c r="B80" s="9" t="n"/>
@@ -1925,12 +1940,12 @@
       <c r="E80" s="9" t="n"/>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="9" t="n"/>
-      <c r="H80" s="22" t="n"/>
-      <c r="I80" s="23" t="n"/>
+      <c r="H80" s="23" t="n"/>
+      <c r="I80" s="24" t="n"/>
       <c r="J80" s="9" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="n">
+      <c r="A81" s="22" t="n">
         <v>75</v>
       </c>
       <c r="B81" s="9" t="n"/>
@@ -1939,12 +1954,12 @@
       <c r="E81" s="9" t="n"/>
       <c r="F81" s="9" t="n"/>
       <c r="G81" s="9" t="n"/>
-      <c r="H81" s="22" t="n"/>
-      <c r="I81" s="23" t="n"/>
+      <c r="H81" s="23" t="n"/>
+      <c r="I81" s="24" t="n"/>
       <c r="J81" s="9" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="11" t="n">
+      <c r="A82" s="22" t="n">
         <v>76</v>
       </c>
       <c r="B82" s="9" t="n"/>
@@ -1953,12 +1968,12 @@
       <c r="E82" s="9" t="n"/>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="9" t="n"/>
-      <c r="H82" s="22" t="n"/>
-      <c r="I82" s="23" t="n"/>
+      <c r="H82" s="23" t="n"/>
+      <c r="I82" s="24" t="n"/>
       <c r="J82" s="9" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="11" t="n">
+      <c r="A83" s="22" t="n">
         <v>77</v>
       </c>
       <c r="B83" s="9" t="n"/>
@@ -1967,12 +1982,12 @@
       <c r="E83" s="9" t="n"/>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="9" t="n"/>
-      <c r="H83" s="22" t="n"/>
-      <c r="I83" s="23" t="n"/>
+      <c r="H83" s="23" t="n"/>
+      <c r="I83" s="24" t="n"/>
       <c r="J83" s="9" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="11" t="n">
+      <c r="A84" s="22" t="n">
         <v>78</v>
       </c>
       <c r="B84" s="9" t="n"/>
@@ -1981,12 +1996,12 @@
       <c r="E84" s="9" t="n"/>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="9" t="n"/>
-      <c r="H84" s="22" t="n"/>
-      <c r="I84" s="23" t="n"/>
+      <c r="H84" s="23" t="n"/>
+      <c r="I84" s="24" t="n"/>
       <c r="J84" s="9" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="11" t="n">
+      <c r="A85" s="22" t="n">
         <v>79</v>
       </c>
       <c r="B85" s="9" t="n"/>
@@ -1995,12 +2010,12 @@
       <c r="E85" s="9" t="n"/>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="9" t="n"/>
-      <c r="H85" s="22" t="n"/>
-      <c r="I85" s="23" t="n"/>
+      <c r="H85" s="23" t="n"/>
+      <c r="I85" s="24" t="n"/>
       <c r="J85" s="9" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="11" t="n">
+      <c r="A86" s="22" t="n">
         <v>80</v>
       </c>
       <c r="B86" s="9" t="n"/>
@@ -2009,12 +2024,12 @@
       <c r="E86" s="9" t="n"/>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="9" t="n"/>
-      <c r="H86" s="22" t="n"/>
-      <c r="I86" s="23" t="n"/>
+      <c r="H86" s="23" t="n"/>
+      <c r="I86" s="24" t="n"/>
       <c r="J86" s="9" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="n">
+      <c r="A87" s="22" t="n">
         <v>81</v>
       </c>
       <c r="B87" s="9" t="n"/>
@@ -2023,12 +2038,12 @@
       <c r="E87" s="9" t="n"/>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="9" t="n"/>
-      <c r="H87" s="22" t="n"/>
-      <c r="I87" s="23" t="n"/>
+      <c r="H87" s="23" t="n"/>
+      <c r="I87" s="24" t="n"/>
       <c r="J87" s="9" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="11" t="n">
+      <c r="A88" s="22" t="n">
         <v>82</v>
       </c>
       <c r="B88" s="9" t="n"/>
@@ -2037,12 +2052,12 @@
       <c r="E88" s="9" t="n"/>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="9" t="n"/>
-      <c r="H88" s="22" t="n"/>
-      <c r="I88" s="23" t="n"/>
+      <c r="H88" s="23" t="n"/>
+      <c r="I88" s="24" t="n"/>
       <c r="J88" s="9" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="11" t="n">
+      <c r="A89" s="22" t="n">
         <v>83</v>
       </c>
       <c r="B89" s="9" t="n"/>
@@ -2051,12 +2066,12 @@
       <c r="E89" s="9" t="n"/>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="9" t="n"/>
-      <c r="H89" s="22" t="n"/>
-      <c r="I89" s="23" t="n"/>
+      <c r="H89" s="23" t="n"/>
+      <c r="I89" s="24" t="n"/>
       <c r="J89" s="9" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="11" t="n">
+      <c r="A90" s="22" t="n">
         <v>84</v>
       </c>
       <c r="B90" s="9" t="n"/>
@@ -2065,12 +2080,12 @@
       <c r="E90" s="9" t="n"/>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="9" t="n"/>
-      <c r="H90" s="22" t="n"/>
-      <c r="I90" s="23" t="n"/>
+      <c r="H90" s="23" t="n"/>
+      <c r="I90" s="24" t="n"/>
       <c r="J90" s="9" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="11" t="n">
+      <c r="A91" s="22" t="n">
         <v>85</v>
       </c>
       <c r="B91" s="9" t="n"/>
@@ -2079,12 +2094,12 @@
       <c r="E91" s="9" t="n"/>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="9" t="n"/>
-      <c r="H91" s="22" t="n"/>
-      <c r="I91" s="23" t="n"/>
+      <c r="H91" s="23" t="n"/>
+      <c r="I91" s="24" t="n"/>
       <c r="J91" s="9" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="n">
+      <c r="A92" s="22" t="n">
         <v>86</v>
       </c>
       <c r="B92" s="9" t="n"/>
@@ -2093,12 +2108,12 @@
       <c r="E92" s="9" t="n"/>
       <c r="F92" s="9" t="n"/>
       <c r="G92" s="9" t="n"/>
-      <c r="H92" s="22" t="n"/>
-      <c r="I92" s="23" t="n"/>
+      <c r="H92" s="23" t="n"/>
+      <c r="I92" s="24" t="n"/>
       <c r="J92" s="9" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="11" t="n">
+      <c r="A93" s="22" t="n">
         <v>87</v>
       </c>
       <c r="B93" s="9" t="n"/>
@@ -2107,12 +2122,12 @@
       <c r="E93" s="9" t="n"/>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="9" t="n"/>
-      <c r="H93" s="22" t="n"/>
-      <c r="I93" s="23" t="n"/>
+      <c r="H93" s="23" t="n"/>
+      <c r="I93" s="24" t="n"/>
       <c r="J93" s="9" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="11" t="n">
+      <c r="A94" s="22" t="n">
         <v>88</v>
       </c>
       <c r="B94" s="9" t="n"/>
@@ -2121,12 +2136,12 @@
       <c r="E94" s="9" t="n"/>
       <c r="F94" s="9" t="n"/>
       <c r="G94" s="9" t="n"/>
-      <c r="H94" s="22" t="n"/>
-      <c r="I94" s="23" t="n"/>
+      <c r="H94" s="23" t="n"/>
+      <c r="I94" s="24" t="n"/>
       <c r="J94" s="9" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="n">
+      <c r="A95" s="22" t="n">
         <v>89</v>
       </c>
       <c r="B95" s="9" t="n"/>
@@ -2135,12 +2150,12 @@
       <c r="E95" s="9" t="n"/>
       <c r="F95" s="9" t="n"/>
       <c r="G95" s="9" t="n"/>
-      <c r="H95" s="22" t="n"/>
-      <c r="I95" s="23" t="n"/>
+      <c r="H95" s="23" t="n"/>
+      <c r="I95" s="24" t="n"/>
       <c r="J95" s="9" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="11" t="n">
+      <c r="A96" s="22" t="n">
         <v>90</v>
       </c>
       <c r="B96" s="9" t="n"/>
@@ -2149,12 +2164,12 @@
       <c r="E96" s="9" t="n"/>
       <c r="F96" s="9" t="n"/>
       <c r="G96" s="9" t="n"/>
-      <c r="H96" s="22" t="n"/>
-      <c r="I96" s="23" t="n"/>
+      <c r="H96" s="23" t="n"/>
+      <c r="I96" s="24" t="n"/>
       <c r="J96" s="9" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="11" t="n">
+      <c r="A97" s="22" t="n">
         <v>91</v>
       </c>
       <c r="B97" s="9" t="n"/>
@@ -2163,12 +2178,12 @@
       <c r="E97" s="9" t="n"/>
       <c r="F97" s="9" t="n"/>
       <c r="G97" s="9" t="n"/>
-      <c r="H97" s="22" t="n"/>
-      <c r="I97" s="23" t="n"/>
+      <c r="H97" s="23" t="n"/>
+      <c r="I97" s="24" t="n"/>
       <c r="J97" s="9" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="11" t="n">
+      <c r="A98" s="22" t="n">
         <v>92</v>
       </c>
       <c r="B98" s="9" t="n"/>
@@ -2177,12 +2192,12 @@
       <c r="E98" s="9" t="n"/>
       <c r="F98" s="9" t="n"/>
       <c r="G98" s="9" t="n"/>
-      <c r="H98" s="22" t="n"/>
-      <c r="I98" s="23" t="n"/>
+      <c r="H98" s="23" t="n"/>
+      <c r="I98" s="24" t="n"/>
       <c r="J98" s="9" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="11" t="n">
+      <c r="A99" s="22" t="n">
         <v>93</v>
       </c>
       <c r="B99" s="9" t="n"/>
@@ -2191,12 +2206,12 @@
       <c r="E99" s="9" t="n"/>
       <c r="F99" s="9" t="n"/>
       <c r="G99" s="9" t="n"/>
-      <c r="H99" s="22" t="n"/>
-      <c r="I99" s="23" t="n"/>
+      <c r="H99" s="23" t="n"/>
+      <c r="I99" s="24" t="n"/>
       <c r="J99" s="9" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="n">
+      <c r="A100" s="22" t="n">
         <v>94</v>
       </c>
       <c r="B100" s="9" t="n"/>
@@ -2205,12 +2220,12 @@
       <c r="E100" s="9" t="n"/>
       <c r="F100" s="9" t="n"/>
       <c r="G100" s="9" t="n"/>
-      <c r="H100" s="22" t="n"/>
-      <c r="I100" s="23" t="n"/>
+      <c r="H100" s="23" t="n"/>
+      <c r="I100" s="24" t="n"/>
       <c r="J100" s="9" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="n">
+      <c r="A101" s="22" t="n">
         <v>95</v>
       </c>
       <c r="B101" s="9" t="n"/>
@@ -2219,12 +2234,12 @@
       <c r="E101" s="9" t="n"/>
       <c r="F101" s="9" t="n"/>
       <c r="G101" s="9" t="n"/>
-      <c r="H101" s="22" t="n"/>
-      <c r="I101" s="23" t="n"/>
+      <c r="H101" s="23" t="n"/>
+      <c r="I101" s="24" t="n"/>
       <c r="J101" s="9" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="n">
+      <c r="A102" s="22" t="n">
         <v>96</v>
       </c>
       <c r="B102" s="9" t="n"/>
@@ -2233,12 +2248,12 @@
       <c r="E102" s="9" t="n"/>
       <c r="F102" s="9" t="n"/>
       <c r="G102" s="9" t="n"/>
-      <c r="H102" s="22" t="n"/>
-      <c r="I102" s="23" t="n"/>
+      <c r="H102" s="23" t="n"/>
+      <c r="I102" s="24" t="n"/>
       <c r="J102" s="9" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="n">
+      <c r="A103" s="22" t="n">
         <v>97</v>
       </c>
       <c r="B103" s="9" t="n"/>
@@ -2247,12 +2262,12 @@
       <c r="E103" s="9" t="n"/>
       <c r="F103" s="9" t="n"/>
       <c r="G103" s="9" t="n"/>
-      <c r="H103" s="22" t="n"/>
-      <c r="I103" s="23" t="n"/>
+      <c r="H103" s="23" t="n"/>
+      <c r="I103" s="24" t="n"/>
       <c r="J103" s="9" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="11" t="n">
+      <c r="A104" s="22" t="n">
         <v>98</v>
       </c>
       <c r="B104" s="9" t="n"/>
@@ -2261,12 +2276,12 @@
       <c r="E104" s="9" t="n"/>
       <c r="F104" s="9" t="n"/>
       <c r="G104" s="9" t="n"/>
-      <c r="H104" s="22" t="n"/>
-      <c r="I104" s="23" t="n"/>
+      <c r="H104" s="23" t="n"/>
+      <c r="I104" s="24" t="n"/>
       <c r="J104" s="9" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="n">
+      <c r="A105" s="22" t="n">
         <v>99</v>
       </c>
       <c r="B105" s="9" t="n"/>
@@ -2275,12 +2290,12 @@
       <c r="E105" s="9" t="n"/>
       <c r="F105" s="9" t="n"/>
       <c r="G105" s="9" t="n"/>
-      <c r="H105" s="22" t="n"/>
-      <c r="I105" s="23" t="n"/>
+      <c r="H105" s="23" t="n"/>
+      <c r="I105" s="24" t="n"/>
       <c r="J105" s="9" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="11" t="n">
+      <c r="A106" s="22" t="n">
         <v>100</v>
       </c>
       <c r="B106" s="9" t="n"/>
@@ -2289,11 +2304,12 @@
       <c r="E106" s="9" t="n"/>
       <c r="F106" s="9" t="n"/>
       <c r="G106" s="9" t="n"/>
-      <c r="H106" s="22" t="n"/>
-      <c r="I106" s="23" t="n"/>
+      <c r="H106" s="23" t="n"/>
+      <c r="I106" s="24" t="n"/>
       <c r="J106" s="9" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A6:J106"/>
   <mergeCells count="4">
     <mergeCell ref="A1:I1"/>

--- a/plantillas/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores.xlsx
@@ -53,7 +53,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -63,7 +63,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -105,7 +105,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -128,7 +128,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -156,7 +156,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -584,7 +584,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="1B6B73"/>
+                <a:srgbClr val="0E7C8B"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -6325,7 +6325,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/plantillas/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores.xlsx
+++ b/plantillas/1_Contabilidad_y_Finanzas/08_Directorio_Clientes_y_Proveedores.xlsx
@@ -984,7 +984,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1451,7 +1451,7 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="C37" s="4" t="n"/>
